--- a/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-Medication.xlsx
+++ b/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-Medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7372" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7360" uniqueCount="719">
   <si>
     <t>Property</t>
   </si>
@@ -442,7 +442,7 @@
     <t>Medication.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -480,7 +480,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -514,7 +514,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -557,7 +557,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -592,10 +592,6 @@
     <t>Medication.contained</t>
   </si>
   <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
     <t xml:space="preserve">Medication {https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pharmaceutical-product|https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pzn-ingredient}
 </t>
   </si>
@@ -603,25 +599,22 @@
     <t>Contains PZN Ingredients for Compounding Medications &amp; PharmaceuticalProducts in case of a 'Kombipackung'</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
     <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>Medication.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Medication.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
   </si>
   <si>
     <t>Medication.extension:rxPrescriptionProcessIdentifier</t>
@@ -935,9 +928,6 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
     <t>Information on the packaging of a formulation.</t>
   </si>
   <si>
@@ -1088,12 +1078,6 @@
   <si>
     <t xml:space="preserve">Identifier {https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-unique-identifier}
 </t>
-  </si>
-  <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
   </si>
   <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
@@ -1135,7 +1119,7 @@
     <t>A coded concept that defines the type of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -1355,7 +1339,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1425,7 +1409,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1482,7 +1466,7 @@
     <t>A coded concept defining the form of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-form-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-form-codes|4.0.1</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -1932,7 +1916,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance|Medication)</t>
+Reference(Substance|4.0.1|Medication|4.0.1)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -1946,6 +1930,9 @@
   <si>
     <t xml:space="preserve">type:$this}
 </t>
+  </si>
+  <si>
+    <t>closed</t>
   </si>
   <si>
     <t>.player</t>
@@ -2596,7 +2583,7 @@
     <col min="1" max="1" width="64.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.42578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="25.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -4355,7 +4342,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4374,16 +4361,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4433,7 +4420,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4448,10 +4435,10 @@
         <v>77</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -4462,10 +4449,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4494,7 +4481,7 @@
         <v>109</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>111</v>
@@ -4547,7 +4534,7 @@
         <v>114</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4565,7 +4552,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -4576,16 +4563,16 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4604,17 +4591,15 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -4663,7 +4648,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4672,7 +4657,7 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>116</v>
@@ -4681,7 +4666,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -4692,16 +4677,16 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4720,17 +4705,15 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4779,7 +4762,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4788,7 +4771,7 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
@@ -4797,7 +4780,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4808,10 +4791,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4920,10 +4903,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4949,10 +4932,10 @@
         <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5032,10 +5015,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5061,13 +5044,13 @@
         <v>129</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5075,7 +5058,7 @@
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>77</v>
@@ -5117,7 +5100,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>87</v>
@@ -5135,7 +5118,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -5146,10 +5129,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5172,13 +5155,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5229,7 +5212,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5247,7 +5230,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -5258,16 +5241,16 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5286,17 +5269,15 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -5345,7 +5326,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5354,7 +5335,7 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>116</v>
@@ -5363,7 +5344,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -5374,10 +5355,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5486,10 +5467,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5515,10 +5496,10 @@
         <v>108</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5598,10 +5579,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5627,13 +5608,13 @@
         <v>129</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5641,7 +5622,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>77</v>
@@ -5683,7 +5664,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>87</v>
@@ -5701,7 +5682,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5712,10 +5693,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5741,10 +5722,10 @@
         <v>141</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5771,11 +5752,11 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -5793,7 +5774,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5811,7 +5792,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5822,10 +5803,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5934,10 +5915,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6048,10 +6029,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6077,16 +6058,16 @@
         <v>129</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -6135,7 +6116,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6153,21 +6134,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6193,13 +6174,13 @@
         <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6249,7 +6230,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6267,21 +6248,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6307,14 +6288,14 @@
         <v>166</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -6363,7 +6344,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6381,21 +6362,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6421,16 +6402,16 @@
         <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6479,7 +6460,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6497,21 +6478,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6534,19 +6515,19 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -6595,7 +6576,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6613,27 +6594,27 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6652,17 +6633,15 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L36" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6711,7 +6690,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6720,7 +6699,7 @@
         <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>116</v>
@@ -6729,7 +6708,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6740,10 +6719,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6852,10 +6831,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6966,10 +6945,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6995,13 +6974,13 @@
         <v>129</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7009,7 +6988,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>77</v>
@@ -7051,7 +7030,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>87</v>
@@ -7069,7 +7048,7 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -7080,10 +7059,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7109,10 +7088,10 @@
         <v>166</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7139,11 +7118,11 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -7161,7 +7140,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7179,7 +7158,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -7190,16 +7169,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7218,17 +7197,15 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>294</v>
+        <v>194</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -7277,7 +7254,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7286,7 +7263,7 @@
         <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>116</v>
@@ -7295,7 +7272,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -7306,10 +7283,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7418,14 +7395,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7447,14 +7424,12 @@
         <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -7521,7 +7496,7 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -7532,10 +7507,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7561,13 +7536,13 @@
         <v>129</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7575,7 +7550,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>77</v>
@@ -7617,7 +7592,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -7635,7 +7610,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -7646,10 +7621,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7675,10 +7650,10 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7702,7 +7677,7 @@
         <v>77</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="X45" t="s" s="2">
         <v>77</v>
@@ -7729,7 +7704,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7747,7 +7722,7 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7758,16 +7733,16 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7786,17 +7761,15 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7845,7 +7818,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7854,7 +7827,7 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>116</v>
@@ -7863,7 +7836,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7874,10 +7847,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7986,10 +7959,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8015,10 +7988,10 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8098,10 +8071,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8127,13 +8100,13 @@
         <v>129</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8141,7 +8114,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>77</v>
@@ -8183,7 +8156,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>87</v>
@@ -8201,7 +8174,7 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -8212,10 +8185,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8241,10 +8214,10 @@
         <v>101</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8268,7 +8241,7 @@
         <v>77</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="X50" t="s" s="2">
         <v>77</v>
@@ -8295,7 +8268,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8313,7 +8286,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -8324,16 +8297,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8352,17 +8325,15 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -8411,7 +8382,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8420,7 +8391,7 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>116</v>
@@ -8429,7 +8400,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -8440,13 +8411,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>77</v>
@@ -8468,13 +8439,13 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8525,7 +8496,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8554,13 +8525,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>77</v>
@@ -8582,13 +8553,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8639,7 +8610,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8668,10 +8639,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8697,16 +8668,16 @@
         <v>108</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8755,7 +8726,7 @@
         <v>114</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8773,7 +8744,7 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -8784,10 +8755,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8810,16 +8781,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8857,7 +8828,7 @@
         <v>77</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -8867,7 +8838,7 @@
         <v>114</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8885,24 +8856,24 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
@@ -8924,16 +8895,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8944,7 +8915,7 @@
         <v>77</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>77</v>
@@ -8983,7 +8954,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9001,24 +8972,24 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -9040,16 +9011,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9060,7 +9031,7 @@
         <v>77</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>77</v>
@@ -9099,7 +9070,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9117,21 +9088,21 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9154,16 +9125,16 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9192,10 +9163,10 @@
         <v>156</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -9213,7 +9184,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9228,24 +9199,24 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9354,10 +9325,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9468,10 +9439,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9497,16 +9468,16 @@
         <v>141</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9543,7 +9514,7 @@
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AC61" s="2"/>
       <c r="AD61" t="s" s="2">
@@ -9553,7 +9524,7 @@
         <v>114</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9571,24 +9542,24 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>77</v>
@@ -9613,16 +9584,16 @@
         <v>141</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9632,7 +9603,7 @@
         <v>77</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>77</v>
@@ -9671,7 +9642,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9689,21 +9660,21 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9812,10 +9783,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9926,10 +9897,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9955,16 +9926,16 @@
         <v>129</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -10013,7 +9984,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10031,21 +10002,21 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10071,13 +10042,13 @@
         <v>101</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10127,7 +10098,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10145,21 +10116,21 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10185,14 +10156,14 @@
         <v>166</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -10241,7 +10212,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10259,21 +10230,21 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10299,16 +10270,16 @@
         <v>101</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -10357,7 +10328,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10375,21 +10346,21 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10412,19 +10383,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -10473,7 +10444,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10491,24 +10462,24 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>77</v>
@@ -10533,16 +10504,16 @@
         <v>141</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -10552,7 +10523,7 @@
         <v>77</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>77</v>
@@ -10591,7 +10562,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10609,21 +10580,21 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10732,10 +10703,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10846,10 +10817,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10875,16 +10846,16 @@
         <v>129</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10933,7 +10904,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10951,21 +10922,21 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10991,13 +10962,13 @@
         <v>101</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11047,7 +11018,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11065,21 +11036,21 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11105,14 +11076,14 @@
         <v>166</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11161,7 +11132,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11179,21 +11150,21 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11219,16 +11190,16 @@
         <v>101</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -11277,7 +11248,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11295,21 +11266,21 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11332,19 +11303,19 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -11393,7 +11364,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11411,24 +11382,24 @@
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>77</v>
@@ -11453,16 +11424,16 @@
         <v>141</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11472,7 +11443,7 @@
         <v>77</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>77</v>
@@ -11511,7 +11482,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11529,21 +11500,21 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11652,10 +11623,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11766,10 +11737,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11795,16 +11766,16 @@
         <v>129</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11853,7 +11824,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11871,21 +11842,21 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11911,13 +11882,13 @@
         <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11967,7 +11938,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11985,21 +11956,21 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12025,14 +11996,14 @@
         <v>166</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -12081,7 +12052,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12099,21 +12070,21 @@
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12139,16 +12110,16 @@
         <v>101</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -12197,7 +12168,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12215,21 +12186,21 @@
         <v>77</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12252,19 +12223,19 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -12313,7 +12284,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12331,21 +12302,21 @@
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12371,16 +12342,16 @@
         <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -12429,7 +12400,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12447,21 +12418,21 @@
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12487,13 +12458,13 @@
         <v>166</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12519,13 +12490,13 @@
         <v>77</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>77</v>
@@ -12543,7 +12514,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12561,7 +12532,7 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -12572,10 +12543,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12598,16 +12569,16 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12657,7 +12628,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12669,27 +12640,27 @@
         <v>149</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12798,10 +12769,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12912,10 +12883,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12941,13 +12912,13 @@
         <v>101</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12997,7 +12968,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13006,7 +12977,7 @@
         <v>87</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>99</v>
@@ -13015,7 +12986,7 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
@@ -13026,10 +12997,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13055,13 +13026,13 @@
         <v>129</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13090,10 +13061,10 @@
         <v>145</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -13111,7 +13082,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13129,7 +13100,7 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -13140,10 +13111,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13166,16 +13137,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13225,7 +13196,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13243,21 +13214,21 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13283,13 +13254,13 @@
         <v>101</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13339,7 +13310,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13357,7 +13328,7 @@
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -13368,10 +13339,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13394,16 +13365,16 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13432,10 +13403,10 @@
         <v>156</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>77</v>
@@ -13453,7 +13424,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13468,24 +13439,24 @@
         <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13594,10 +13565,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13708,10 +13679,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13737,16 +13708,16 @@
         <v>141</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13783,7 +13754,7 @@
         <v>77</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
@@ -13793,7 +13764,7 @@
         <v>114</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13811,24 +13782,24 @@
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>77</v>
@@ -13853,16 +13824,16 @@
         <v>141</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>77</v>
@@ -13872,7 +13843,7 @@
         <v>77</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>77</v>
@@ -13887,11 +13858,11 @@
         <v>77</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>77</v>
@@ -13909,7 +13880,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13927,21 +13898,21 @@
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14050,10 +14021,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14164,10 +14135,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14193,16 +14164,16 @@
         <v>129</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N102" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -14251,7 +14222,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14269,21 +14240,21 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14309,13 +14280,13 @@
         <v>101</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14365,7 +14336,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14383,21 +14354,21 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14423,14 +14394,14 @@
         <v>166</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -14479,7 +14450,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14497,21 +14468,21 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14537,16 +14508,16 @@
         <v>101</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -14595,7 +14566,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14613,21 +14584,21 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14650,19 +14621,19 @@
         <v>88</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N106" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>77</v>
@@ -14711,7 +14682,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14729,21 +14700,21 @@
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14769,16 +14740,16 @@
         <v>101</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -14827,7 +14798,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14845,21 +14816,21 @@
         <v>77</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14882,16 +14853,16 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14941,7 +14912,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14953,27 +14924,27 @@
         <v>149</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15082,10 +15053,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15196,10 +15167,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15222,16 +15193,16 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15261,7 +15232,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>77</v>
@@ -15279,7 +15250,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15291,27 +15262,27 @@
         <v>149</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15420,10 +15391,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15534,16 +15505,16 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15562,17 +15533,15 @@
         <v>77</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>77</v>
@@ -15630,7 +15599,7 @@
         <v>79</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>116</v>
@@ -15639,7 +15608,7 @@
         <v>77</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>77</v>
@@ -15650,10 +15619,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15762,10 +15731,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15791,10 +15760,10 @@
         <v>108</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15874,10 +15843,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15903,13 +15872,13 @@
         <v>129</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N117" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15917,7 +15886,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>77</v>
@@ -15959,7 +15928,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>87</v>
@@ -15977,7 +15946,7 @@
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
@@ -15988,10 +15957,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16017,10 +15986,10 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16044,7 +16013,7 @@
         <v>77</v>
       </c>
       <c r="W118" t="s" s="2">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="X118" t="s" s="2">
         <v>77</v>
@@ -16071,7 +16040,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16089,7 +16058,7 @@
         <v>77</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>77</v>
@@ -16100,16 +16069,16 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16128,17 +16097,15 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -16196,7 +16163,7 @@
         <v>79</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>116</v>
@@ -16205,7 +16172,7 @@
         <v>77</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
@@ -16216,10 +16183,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16328,10 +16295,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16357,10 +16324,10 @@
         <v>108</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16440,10 +16407,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16469,13 +16436,13 @@
         <v>129</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N122" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16483,7 +16450,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>77</v>
@@ -16525,7 +16492,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>87</v>
@@ -16543,7 +16510,7 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -16554,10 +16521,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16583,10 +16550,10 @@
         <v>101</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16610,7 +16577,7 @@
         <v>77</v>
       </c>
       <c r="W123" t="s" s="2">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="X123" t="s" s="2">
         <v>77</v>
@@ -16637,7 +16604,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16655,7 +16622,7 @@
         <v>77</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>77</v>
@@ -16666,10 +16633,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16692,19 +16659,19 @@
         <v>88</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>77</v>
@@ -16753,7 +16720,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16771,21 +16738,21 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16811,20 +16778,20 @@
         <v>166</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q125" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="R125" t="s" s="2">
         <v>77</v>
@@ -16845,13 +16812,13 @@
         <v>77</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>77</v>
@@ -16869,7 +16836,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16887,21 +16854,21 @@
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16927,16 +16894,16 @@
         <v>101</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -16985,7 +16952,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17003,21 +16970,21 @@
         <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17043,16 +17010,16 @@
         <v>129</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>77</v>
@@ -17101,7 +17068,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17110,7 +17077,7 @@
         <v>87</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>99</v>
@@ -17119,21 +17086,21 @@
         <v>77</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17159,16 +17126,16 @@
         <v>166</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>77</v>
@@ -17217,7 +17184,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17235,21 +17202,21 @@
         <v>77</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17272,16 +17239,16 @@
         <v>88</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17311,7 +17278,7 @@
       </c>
       <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>77</v>
@@ -17329,7 +17296,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17341,27 +17308,27 @@
         <v>149</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17470,10 +17437,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17584,10 +17551,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17610,19 +17577,19 @@
         <v>88</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -17671,7 +17638,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17689,21 +17656,21 @@
         <v>77</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17729,20 +17696,20 @@
         <v>166</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q133" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="R133" t="s" s="2">
         <v>77</v>
@@ -17763,13 +17730,13 @@
         <v>77</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>77</v>
@@ -17787,7 +17754,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17805,21 +17772,21 @@
         <v>77</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17845,16 +17812,16 @@
         <v>101</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>77</v>
@@ -17903,7 +17870,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17921,21 +17888,21 @@
         <v>77</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17961,16 +17928,16 @@
         <v>129</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
@@ -18019,7 +17986,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18028,7 +17995,7 @@
         <v>87</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>99</v>
@@ -18037,21 +18004,21 @@
         <v>77</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18077,16 +18044,16 @@
         <v>166</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>77</v>
@@ -18135,7 +18102,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -18153,21 +18120,21 @@
         <v>77</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18190,16 +18157,16 @@
         <v>77</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18249,7 +18216,7 @@
         <v>77</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -18267,7 +18234,7 @@
         <v>77</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>77</v>
@@ -18278,10 +18245,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18390,10 +18357,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18504,16 +18471,16 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18532,17 +18499,15 @@
         <v>77</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>77</v>
@@ -18600,7 +18565,7 @@
         <v>79</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>116</v>
@@ -18609,7 +18574,7 @@
         <v>77</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
@@ -18620,14 +18585,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -18649,16 +18614,16 @@
         <v>108</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>77</v>
@@ -18707,7 +18672,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18725,7 +18690,7 @@
         <v>77</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>77</v>
@@ -18736,10 +18701,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18762,17 +18727,17 @@
         <v>77</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>77</v>
@@ -18809,17 +18774,17 @@
         <v>77</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="AC142" s="2"/>
       <c r="AD142" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>87</v>
@@ -18834,27 +18799,27 @@
         <v>99</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>77</v>
@@ -18876,17 +18841,17 @@
         <v>77</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>77</v>
@@ -18935,7 +18900,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>87</v>
@@ -18950,24 +18915,24 @@
         <v>99</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19076,10 +19041,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19190,10 +19155,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19219,16 +19184,16 @@
         <v>141</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>77</v>
@@ -19265,7 +19230,7 @@
         <v>77</v>
       </c>
       <c r="AB146" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AC146" s="2"/>
       <c r="AD146" t="s" s="2">
@@ -19275,7 +19240,7 @@
         <v>114</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -19293,24 +19258,24 @@
         <v>77</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D147" t="s" s="2">
         <v>77</v>
@@ -19335,16 +19300,16 @@
         <v>141</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>77</v>
@@ -19354,7 +19319,7 @@
         <v>77</v>
       </c>
       <c r="S147" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="T147" t="s" s="2">
         <v>77</v>
@@ -19393,7 +19358,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19411,21 +19376,21 @@
         <v>77</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19534,10 +19499,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19648,10 +19613,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19677,16 +19642,16 @@
         <v>129</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N150" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="O150" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>77</v>
@@ -19735,7 +19700,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19753,21 +19718,21 @@
         <v>77</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19793,13 +19758,13 @@
         <v>101</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N151" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -19849,7 +19814,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19867,21 +19832,21 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19907,14 +19872,14 @@
         <v>166</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>77</v>
@@ -19963,7 +19928,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19981,21 +19946,21 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20021,16 +19986,16 @@
         <v>101</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N153" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>77</v>
@@ -20079,7 +20044,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -20097,21 +20062,21 @@
         <v>77</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20134,19 +20099,19 @@
         <v>88</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N154" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="O154" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>77</v>
@@ -20195,7 +20160,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -20213,24 +20178,24 @@
         <v>77</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D155" t="s" s="2">
         <v>77</v>
@@ -20255,16 +20220,16 @@
         <v>141</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>77</v>
@@ -20274,7 +20239,7 @@
         <v>77</v>
       </c>
       <c r="S155" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="T155" t="s" s="2">
         <v>77</v>
@@ -20313,7 +20278,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -20331,21 +20296,21 @@
         <v>77</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20454,10 +20419,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20568,10 +20533,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20597,16 +20562,16 @@
         <v>129</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N158" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="O158" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>77</v>
@@ -20655,7 +20620,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20673,21 +20638,21 @@
         <v>77</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20713,13 +20678,13 @@
         <v>101</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N159" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -20769,7 +20734,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20787,21 +20752,21 @@
         <v>77</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20827,14 +20792,14 @@
         <v>166</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>77</v>
@@ -20883,7 +20848,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20901,21 +20866,21 @@
         <v>77</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20941,16 +20906,16 @@
         <v>101</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N161" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="O161" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>77</v>
@@ -20999,7 +20964,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -21017,21 +20982,21 @@
         <v>77</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21054,19 +21019,19 @@
         <v>88</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N162" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="O162" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>77</v>
@@ -21115,7 +21080,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -21133,24 +21098,24 @@
         <v>77</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>77</v>
@@ -21175,16 +21140,16 @@
         <v>141</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>77</v>
@@ -21194,7 +21159,7 @@
         <v>77</v>
       </c>
       <c r="S163" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="T163" t="s" s="2">
         <v>77</v>
@@ -21233,7 +21198,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21251,21 +21216,21 @@
         <v>77</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21374,10 +21339,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21488,10 +21453,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21517,16 +21482,16 @@
         <v>129</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N166" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M166" t="s" s="2">
+      <c r="O166" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>77</v>
@@ -21575,7 +21540,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -21593,21 +21558,21 @@
         <v>77</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21633,13 +21598,13 @@
         <v>101</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -21689,7 +21654,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -21707,21 +21672,21 @@
         <v>77</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21747,14 +21712,14 @@
         <v>166</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>77</v>
@@ -21803,7 +21768,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -21821,21 +21786,21 @@
         <v>77</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21861,16 +21826,16 @@
         <v>101</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N169" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>77</v>
@@ -21919,7 +21884,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -21937,21 +21902,21 @@
         <v>77</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21974,19 +21939,19 @@
         <v>88</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M170" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N170" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="O170" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>77</v>
@@ -22035,7 +22000,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -22053,21 +22018,21 @@
         <v>77</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22093,16 +22058,16 @@
         <v>101</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>77</v>
@@ -22151,7 +22116,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -22169,24 +22134,24 @@
         <v>77</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>77</v>
@@ -22208,17 +22173,17 @@
         <v>77</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>77</v>
@@ -22267,7 +22232,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>87</v>
@@ -22282,24 +22247,24 @@
         <v>99</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22322,17 +22287,17 @@
         <v>77</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>77</v>
@@ -22381,7 +22346,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22399,7 +22364,7 @@
         <v>77</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>77</v>
@@ -22410,10 +22375,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22436,16 +22401,16 @@
         <v>77</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -22495,7 +22460,7 @@
         <v>77</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>78</v>
@@ -22507,27 +22472,27 @@
         <v>149</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="AM174" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22636,10 +22601,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22750,16 +22715,16 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -22778,17 +22743,15 @@
         <v>77</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="N177" s="2"/>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>77</v>
@@ -22846,7 +22809,7 @@
         <v>79</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>116</v>
@@ -22855,7 +22818,7 @@
         <v>77</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>77</v>
@@ -22866,10 +22829,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22978,10 +22941,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23007,10 +22970,10 @@
         <v>108</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23090,10 +23053,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23119,13 +23082,13 @@
         <v>129</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M180" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N180" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -23133,7 +23096,7 @@
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>77</v>
@@ -23175,7 +23138,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>87</v>
@@ -23193,7 +23156,7 @@
         <v>77</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>77</v>
@@ -23204,10 +23167,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23233,10 +23196,10 @@
         <v>101</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -23260,7 +23223,7 @@
         <v>77</v>
       </c>
       <c r="W181" t="s" s="2">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="X181" t="s" s="2">
         <v>77</v>
@@ -23287,7 +23250,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>
@@ -23305,7 +23268,7 @@
         <v>77</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM181" t="s" s="2">
         <v>77</v>
@@ -23316,10 +23279,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23342,16 +23305,16 @@
         <v>88</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -23381,7 +23344,7 @@
       </c>
       <c r="Y182" s="2"/>
       <c r="Z182" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>77</v>
@@ -23399,7 +23362,7 @@
         <v>77</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>78</v>
@@ -23411,27 +23374,27 @@
         <v>149</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23540,10 +23503,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23654,10 +23617,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23680,19 +23643,19 @@
         <v>88</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>77</v>
@@ -23741,7 +23704,7 @@
         <v>77</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>78</v>
@@ -23759,21 +23722,21 @@
         <v>77</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23799,20 +23762,20 @@
         <v>166</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q186" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="R186" t="s" s="2">
         <v>77</v>
@@ -23833,13 +23796,13 @@
         <v>77</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>77</v>
@@ -23857,7 +23820,7 @@
         <v>77</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>78</v>
@@ -23875,21 +23838,21 @@
         <v>77</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23915,16 +23878,16 @@
         <v>101</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>77</v>
@@ -23973,7 +23936,7 @@
         <v>77</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>78</v>
@@ -23991,21 +23954,21 @@
         <v>77</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24031,16 +23994,16 @@
         <v>129</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>77</v>
@@ -24089,7 +24052,7 @@
         <v>77</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>78</v>
@@ -24098,7 +24061,7 @@
         <v>87</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>99</v>
@@ -24107,21 +24070,21 @@
         <v>77</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24147,16 +24110,16 @@
         <v>166</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>77</v>
@@ -24205,7 +24168,7 @@
         <v>77</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>78</v>
@@ -24223,21 +24186,21 @@
         <v>77</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24260,16 +24223,16 @@
         <v>88</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
@@ -24299,7 +24262,7 @@
       </c>
       <c r="Y190" s="2"/>
       <c r="Z190" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>77</v>
@@ -24317,7 +24280,7 @@
         <v>77</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>78</v>
@@ -24329,27 +24292,27 @@
         <v>149</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="AM190" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -24458,10 +24421,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -24572,10 +24535,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -24598,19 +24561,19 @@
         <v>88</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>77</v>
@@ -24659,7 +24622,7 @@
         <v>77</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>78</v>
@@ -24677,21 +24640,21 @@
         <v>77</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24717,20 +24680,20 @@
         <v>166</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q194" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="R194" t="s" s="2">
         <v>77</v>
@@ -24751,13 +24714,13 @@
         <v>77</v>
       </c>
       <c r="X194" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>77</v>
@@ -24775,7 +24738,7 @@
         <v>77</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>78</v>
@@ -24793,21 +24756,21 @@
         <v>77</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24833,16 +24796,16 @@
         <v>101</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>77</v>
@@ -24891,7 +24854,7 @@
         <v>77</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>78</v>
@@ -24909,21 +24872,21 @@
         <v>77</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="AM195" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24949,16 +24912,16 @@
         <v>129</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>77</v>
@@ -25007,7 +24970,7 @@
         <v>77</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>78</v>
@@ -25016,7 +24979,7 @@
         <v>87</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>99</v>
@@ -25025,21 +24988,21 @@
         <v>77</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25065,16 +25028,16 @@
         <v>166</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>77</v>
@@ -25123,7 +25086,7 @@
         <v>77</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>78</v>
@@ -25141,21 +25104,21 @@
         <v>77</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="AM197" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25178,13 +25141,13 @@
         <v>77</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -25235,7 +25198,7 @@
         <v>77</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>78</v>
@@ -25250,10 +25213,10 @@
         <v>99</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>77</v>
@@ -25264,10 +25227,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -25376,10 +25339,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -25490,14 +25453,14 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="E201" s="2"/>
       <c r="F201" t="s" s="2">
@@ -25519,16 +25482,16 @@
         <v>108</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="N201" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>77</v>
@@ -25577,7 +25540,7 @@
         <v>77</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>78</v>
@@ -25595,7 +25558,7 @@
         <v>77</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>77</v>
@@ -25606,10 +25569,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -25635,13 +25598,13 @@
         <v>101</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
@@ -25691,7 +25654,7 @@
         <v>77</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>78</v>
@@ -25706,24 +25669,24 @@
         <v>99</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -25746,13 +25709,13 @@
         <v>77</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -25803,7 +25766,7 @@
         <v>77</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>78</v>
@@ -25818,16 +25781,16 @@
         <v>99</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
